--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>113412255</v>
       </c>
       <c r="B15" t="n">
-        <v>97255</v>
+        <v>97258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>113412255</v>
       </c>
       <c r="B15" t="n">
-        <v>97258</v>
+        <v>97259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>113412255</v>
       </c>
       <c r="B15" t="n">
-        <v>97259</v>
+        <v>97261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>113412255</v>
       </c>
       <c r="B15" t="n">
-        <v>97261</v>
+        <v>97262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -2286,7 +2286,7 @@
         <v>113412255</v>
       </c>
       <c r="B15" t="n">
-        <v>97267</v>
+        <v>97273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -675,47 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113339244</v>
+        <v>113343505</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579872</v>
+        <v>579782</v>
       </c>
       <c r="R2" t="n">
-        <v>6577452</v>
+        <v>6577417</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +752,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +762,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hundratals plantor i kontinuitetsskogen.</t>
+          <t>Växer resupinat på undersidan av gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,61 +794,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113338478</v>
+        <v>113411097</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Amandastugan, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580049</v>
+        <v>579776</v>
       </c>
       <c r="R3" t="n">
-        <v>6577495</v>
+        <v>6577414</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,22 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,81 +890,67 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113342885</v>
+        <v>113418687</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skaluten, Srm</t>
+          <t>Dalhagsskogen, Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579789</v>
+        <v>579737</v>
       </c>
       <c r="R4" t="n">
-        <v>6577483</v>
+        <v>6577449</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,22 +974,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växer på granstubbe i kalkbarrsakog. Kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,8 +1003,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog. Kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1048,60 +1032,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113343505</v>
+        <v>113410989</v>
       </c>
       <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2667</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalhagen, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579782</v>
+        <v>579739</v>
       </c>
       <c r="R5" t="n">
-        <v>6577417</v>
+        <v>6577399</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,27 +1098,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växer resupinat på undersidan av gran.</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,27 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113339180</v>
+        <v>113410089</v>
       </c>
       <c r="B6" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,31 +1151,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1220,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579860</v>
+        <v>579703</v>
       </c>
       <c r="R6" t="n">
-        <v>6577513</v>
+        <v>6577464</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,22 +1208,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,57 +1250,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113341251</v>
+        <v>113412255</v>
       </c>
       <c r="B7" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Amandastugan, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580051</v>
+        <v>580032</v>
       </c>
       <c r="R7" t="n">
-        <v>6577522</v>
+        <v>6577374</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,27 +1316,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer på stenröse i hällmark. Troligen oregistrerad fornlämning.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,27 +1346,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113342823</v>
+        <v>113418612</v>
       </c>
       <c r="B8" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,27 +1369,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1457,17 +1401,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skaluten, Srm</t>
+          <t>Dalhagsskogen, Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579794</v>
+        <v>580005</v>
       </c>
       <c r="R8" t="n">
-        <v>6577479</v>
+        <v>6577473</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,22 +1435,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-21</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer under äldre granar i fuktig lokalmiljö alldeles intill planerad körväg för skogsmaskiner. Skogen är avverkningsanmäld. Kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,8 +1464,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1533,52 +1493,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113388205</v>
+        <v>113411337</v>
       </c>
       <c r="B9" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1586,13 +1531,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579865</v>
+        <v>579858</v>
       </c>
       <c r="R9" t="n">
-        <v>6577448</v>
+        <v>6577387</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,22 +1561,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1658,57 +1603,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113383936</v>
+        <v>113412741</v>
       </c>
       <c r="B10" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalhagen, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580177</v>
+        <v>580024</v>
       </c>
       <c r="R10" t="n">
-        <v>6577372</v>
+        <v>6577488</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1732,22 +1669,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1762,27 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113385385</v>
+        <v>113410004</v>
       </c>
       <c r="B11" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,40 +1722,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Amandastugan, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580044</v>
+        <v>579905</v>
       </c>
       <c r="R11" t="n">
-        <v>6577505</v>
+        <v>6577439</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1847,22 +1777,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,12 +1807,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1892,12 +1822,7 @@
         <v>113398113</v>
       </c>
       <c r="B12" t="n">
-        <v>89787</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1844,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2028,63 +1953,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113388106</v>
+        <v>113418438</v>
       </c>
       <c r="B13" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>2008</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skaluten, Srm</t>
+          <t>Dalhagsskogen, Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579857</v>
+        <v>579875</v>
       </c>
       <c r="R13" t="n">
-        <v>6577474</v>
+        <v>6577417</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2111,22 +2025,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer under gammal gran i lokalt fuktig skogsmiljö.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,8 +2054,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kontunitetsskog. Betespräglad kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2153,66 +2083,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113384816</v>
+        <v>113418492</v>
       </c>
       <c r="B14" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>2008</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Amandastugan, Srm</t>
+          <t>Dalhagsskogen, Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580055</v>
+        <v>579867</v>
       </c>
       <c r="R14" t="n">
-        <v>6577521</v>
+        <v>6577461</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2236,27 +2159,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gnagspår på äldre grov tall.</t>
+          <t>Växer i förnan under granar ca 150 år gamla.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2265,8 +2188,19 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog. Kontinutetsskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2283,49 +2217,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113412255</v>
+        <v>113413187</v>
       </c>
       <c r="B15" t="n">
-        <v>97273</v>
+        <v>92281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
+          <t>Dalhagen, Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580032</v>
+        <v>580123</v>
       </c>
       <c r="R15" t="n">
-        <v>6577374</v>
+        <v>6577362</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2352,26 +2286,16 @@
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2379,27 +2303,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113411830</v>
+        <v>113341251</v>
       </c>
       <c r="B16" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,38 +2326,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Amandastugan, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579876</v>
+        <v>580051</v>
       </c>
       <c r="R16" t="n">
-        <v>6577325</v>
+        <v>6577522</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2462,22 +2384,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Växer på stenröse i hällmark. Troligen oregistrerad fornlämning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2492,27 +2419,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113410045</v>
+        <v>113383936</v>
       </c>
       <c r="B17" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,38 +2442,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579905</v>
+        <v>580177</v>
       </c>
       <c r="R17" t="n">
-        <v>6577439</v>
+        <v>6577372</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2575,22 +2500,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2605,72 +2530,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113418438</v>
+        <v>113409911</v>
       </c>
       <c r="B18" t="n">
-        <v>89787</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2008</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Dalhagen, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579875</v>
+        <v>579905</v>
       </c>
       <c r="R18" t="n">
-        <v>6577417</v>
+        <v>6577439</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2699,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2709,12 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer under gammal gran i lokalt fuktig skogsmiljö.</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,83 +2632,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Kontunitetsskog. Betespräglad kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113409534</v>
+        <v>113385385</v>
       </c>
       <c r="B19" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Amandastugan, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580042</v>
+        <v>580044</v>
       </c>
       <c r="R19" t="n">
-        <v>6577529</v>
+        <v>6577505</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2823,22 +2718,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2853,76 +2748,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113418492</v>
+        <v>113410255</v>
       </c>
       <c r="B20" t="n">
-        <v>89787</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2008</v>
+        <v>3215</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Dalhagen, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579867</v>
+        <v>579905</v>
       </c>
       <c r="R20" t="n">
-        <v>6577461</v>
+        <v>6577439</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2951,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2961,12 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Växer i förnan under granar ca 150 år gamla.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2975,44 +2850,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog. Kontinutetsskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113418687</v>
+        <v>113411578</v>
       </c>
       <c r="B21" t="n">
-        <v>90951</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3020,44 +2879,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1339</v>
+        <v>4189</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Dalhagen, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579737</v>
+        <v>579878</v>
       </c>
       <c r="R21" t="n">
-        <v>6577449</v>
+        <v>6577434</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3086,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3096,12 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Växer på granstubbe i kalkbarrsakog. Kontinuitetsskog.</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,44 +2958,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog. Kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113409911</v>
+        <v>113418659</v>
       </c>
       <c r="B22" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3155,35 +2987,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>4189</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagsskogen, Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579905</v>
+        <v>579829</v>
       </c>
       <c r="R22" t="n">
-        <v>6577439</v>
+        <v>6577423</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3215,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3225,7 +3067,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Växer i förnan under gamla granar intill ett alkärr. Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3234,33 +3081,39 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Betespräglad kalkbarrskog. Kontinuitetsskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113411972</v>
+        <v>113387832</v>
       </c>
       <c r="B23" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3295,17 +3148,17 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dalhagen, Srm</t>
+          <t>Amandastugan, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579983</v>
+        <v>579958</v>
       </c>
       <c r="R23" t="n">
-        <v>6577316</v>
+        <v>6577531</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3329,22 +3182,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Växer på hällmark. Kontinuitetsskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3371,56 +3229,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113410089</v>
+        <v>113387970</v>
       </c>
       <c r="B24" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skaluten, Srm</t>
+          <t>Amandastugan, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579703</v>
+        <v>579917</v>
       </c>
       <c r="R24" t="n">
-        <v>6577464</v>
+        <v>6577536</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3444,22 +3305,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3486,54 +3347,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113410004</v>
+        <v>113409534</v>
       </c>
       <c r="B25" t="n">
-        <v>90951</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1339</v>
+        <v>5966</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579905</v>
+        <v>580042</v>
       </c>
       <c r="R25" t="n">
-        <v>6577439</v>
+        <v>6577529</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3562,7 +3418,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3572,7 +3428,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3599,54 +3455,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113411578</v>
+        <v>113411874</v>
       </c>
       <c r="B26" t="n">
-        <v>89784</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4189</v>
+        <v>5966</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579878</v>
+        <v>579877</v>
       </c>
       <c r="R26" t="n">
-        <v>6577434</v>
+        <v>6577345</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3675,7 +3530,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3685,7 +3540,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3712,59 +3567,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113418624</v>
+        <v>113411972</v>
       </c>
       <c r="B27" t="n">
-        <v>8414</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Närsjöfjärden, Srm</t>
+          <t>Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580033</v>
+        <v>579983</v>
       </c>
       <c r="R27" t="n">
-        <v>6577381</v>
+        <v>6577316</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3796,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3806,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3815,19 +3663,8 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3844,51 +3681,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113413187</v>
+        <v>113414147</v>
       </c>
       <c r="B28" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2062</v>
+        <v>5966</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dalhagen (Dalhagen), Srm</t>
+          <t>Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580123</v>
+        <v>579917</v>
       </c>
       <c r="R28" t="n">
-        <v>6577362</v>
+        <v>6577531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3927,84 +3761,85 @@
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113418659</v>
+        <v>113342885</v>
       </c>
       <c r="B29" t="n">
-        <v>89784</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4189</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Dalhagen, Srm</t>
+          <t>Skaluten, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579829</v>
+        <v>579789</v>
       </c>
       <c r="R29" t="n">
-        <v>6577423</v>
+        <v>6577483</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4028,27 +3863,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Växer i förnan under gamla granar intill ett alkärr. Kalkbarrskog.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4057,19 +3887,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Betespräglad kalkbarrskog. Kontinuitetsskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4086,54 +3905,61 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113411097</v>
+        <v>113384816</v>
       </c>
       <c r="B30" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Amandastugan, Srm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579776</v>
+        <v>580055</v>
       </c>
       <c r="R30" t="n">
-        <v>6577414</v>
+        <v>6577521</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4157,22 +3983,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gnagspår på äldre grov tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4187,68 +4018,73 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113411337</v>
+        <v>113388106</v>
       </c>
       <c r="B31" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dalhagen, Srm</t>
+          <t>Skaluten, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579858</v>
+        <v>579857</v>
       </c>
       <c r="R31" t="n">
-        <v>6577387</v>
+        <v>6577474</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4272,22 +4108,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4314,58 +4150,61 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113411874</v>
+        <v>113388205</v>
       </c>
       <c r="B32" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579877</v>
+        <v>579865</v>
       </c>
       <c r="R32" t="n">
-        <v>6577345</v>
+        <v>6577448</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4389,22 +4228,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4419,68 +4258,61 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113414147</v>
+        <v>113410045</v>
       </c>
       <c r="B33" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dalhagen, Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579917</v>
+        <v>579905</v>
       </c>
       <c r="R33" t="n">
-        <v>6577531</v>
+        <v>6577439</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4507,84 +4339,88 @@
           <t>2023-11-26</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-11-26</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Ella Axelsson Elfving</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113412741</v>
+        <v>113411830</v>
       </c>
       <c r="B34" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagsskogen, Dalhagsskogen, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580024</v>
+        <v>579876</v>
       </c>
       <c r="R34" t="n">
-        <v>6577488</v>
+        <v>6577325</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4613,7 +4449,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4623,7 +4459,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4650,15 +4486,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113410989</v>
+        <v>113418624</v>
       </c>
       <c r="B35" t="n">
-        <v>94158</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4666,38 +4497,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Dalhagsskogen, Närsjöfjärden, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>579739</v>
+        <v>580033</v>
       </c>
       <c r="R35" t="n">
-        <v>6577399</v>
+        <v>6577381</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4726,7 +4565,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4736,7 +4575,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4745,33 +4584,39 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskog.</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113418612</v>
+        <v>113338478</v>
       </c>
       <c r="B36" t="n">
-        <v>94275</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4779,31 +4624,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4811,17 +4652,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dalhagsskogen, Dalhagen, Srm</t>
+          <t>Amandastugan, Srm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580005</v>
+        <v>580049</v>
       </c>
       <c r="R36" t="n">
-        <v>6577473</v>
+        <v>6577495</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4845,27 +4686,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Växer under äldre granar i fuktig lokalmiljö alldeles intill planerad körväg för skogsmaskiner. Skogen är avverkningsanmäld. Kontinuitetsskog.</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4874,19 +4710,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskog.</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4903,60 +4728,56 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113387832</v>
+        <v>113339180</v>
       </c>
       <c r="B37" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Amandastugan, Srm</t>
+          <t>Skaluten, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>579958</v>
+        <v>579860</v>
       </c>
       <c r="R37" t="n">
-        <v>6577531</v>
+        <v>6577513</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4980,27 +4801,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Växer på hällmark. Kontinuitetsskog</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5027,64 +4843,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113387970</v>
+        <v>113339244</v>
       </c>
       <c r="B38" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5966</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Amandastugan, Srm</t>
+          <t>Dalhagen, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>579917</v>
+        <v>579872</v>
       </c>
       <c r="R38" t="n">
-        <v>6577536</v>
+        <v>6577452</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5108,22 +4916,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hundratals plantor i kontinuitetsskogen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5150,15 +4963,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113410255</v>
+        <v>113342823</v>
       </c>
       <c r="B39" t="n">
-        <v>90105</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ej möjlig att validera</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5166,38 +4974,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Dalhagsskogen (Dalhagsskogen), Srm</t>
+          <t>Skaluten, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>579905</v>
+        <v>579794</v>
       </c>
       <c r="R39" t="n">
-        <v>6577439</v>
+        <v>6577479</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5221,22 +5036,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5251,12 +5066,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ella Axelsson Elfving</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 50772-2023 artfynd.xlsx
+++ b/artfynd/A 50772-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113412255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113343505</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,6 +1162,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411097</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411337</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113412741</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113410004</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418687</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1732,6 +1777,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398113</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1862,6 +1912,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418438</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1996,6 +2051,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418492</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2094,6 +2154,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113413187</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2210,6 +2275,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113341251</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2321,6 +2391,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113383936</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2429,6 +2504,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113409911</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2537,6 +2617,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113410989</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2647,6 +2732,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113385385</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2757,6 +2847,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113410089</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2865,6 +2960,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113410255</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2973,6 +3073,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411578</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3107,6 +3212,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418659</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3226,6 +3336,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113387832</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3344,6 +3459,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113387970</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3452,6 +3572,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113409534</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3564,6 +3689,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411874</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3678,6 +3808,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411972</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3779,6 +3914,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113414147</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3902,6 +4042,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113342885</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4027,6 +4172,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113384816</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4147,6 +4297,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113388106</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4267,6 +4422,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113388205</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4375,6 +4535,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113410045</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4483,6 +4648,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113411830</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4610,6 +4780,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113418624</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4725,6 +4900,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113338478</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4840,6 +5020,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113339180</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4960,6 +5145,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113339244</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5075,8 +5265,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113342823</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>